--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104478_W3.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104478_W3.xlsx
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.059900000000001</v>
+        <v>6.5736</v>
       </c>
       <c r="E2" t="n">
-        <v>6.1864</v>
+        <v>5.0448</v>
       </c>
       <c r="F2" t="n">
-        <v>1.8735</v>
+        <v>1.5288</v>
       </c>
       <c r="G2" t="n">
-        <v>3.0087</v>
+        <v>3.0067</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.4027</v>
+        <v>-1.3962</v>
       </c>
       <c r="I2" t="n">
-        <v>4.4114</v>
+        <v>4.4029</v>
       </c>
       <c r="J2" t="n">
-        <v>3.2499</v>
+        <v>3.2205</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.551</v>
+        <v>-0.5623</v>
       </c>
       <c r="L2" t="n">
-        <v>3.8009</v>
+        <v>3.7828</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.2411</v>
+        <v>-0.2138</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.8516</v>
+        <v>-0.8339</v>
       </c>
       <c r="O2" t="n">
-        <v>0.6105</v>
+        <v>0.6201</v>
       </c>
       <c r="P2" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R2" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S2" t="n">
-        <v>1.8243</v>
+        <v>0.3393</v>
       </c>
       <c r="T2" t="n">
-        <v>1.5243</v>
+        <v>0.4177</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3</v>
+        <v>-0.0785</v>
       </c>
       <c r="V2" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="W2" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>F. GUERRA</t>
+          <t>G. SHERMADINI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.8824</v>
+        <v>2.3018</v>
       </c>
       <c r="E3" t="n">
-        <v>1.3999</v>
+        <v>2.3256</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4825</v>
+        <v>-0.0238</v>
       </c>
       <c r="G3" t="n">
-        <v>1.7175</v>
+        <v>1.7127</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7951</v>
+        <v>0.552</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9223</v>
+        <v>1.1607</v>
       </c>
       <c r="J3" t="n">
-        <v>3.0277</v>
+        <v>1.6556</v>
       </c>
       <c r="K3" t="n">
-        <v>2.2441</v>
+        <v>1.5438</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7837</v>
+        <v>0.1117</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.3103</v>
+        <v>0.0572</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.4489</v>
+        <v>-0.9918</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1387</v>
+        <v>1.049</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.4952</v>
+        <v>-1.1382</v>
       </c>
       <c r="R3" t="n">
-        <v>1.8147</v>
+        <v>0.4553</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2991</v>
+        <v>0.7272999999999999</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1603</v>
+        <v>0.174</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1388</v>
+        <v>0.5532</v>
       </c>
       <c r="V3" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="W3" t="n">
-        <v>0.7071</v>
+        <v>1.6342</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.1607</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>G. SHERMADINI</t>
+          <t>M. HUERTAS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.7747</v>
+        <v>1.7006</v>
       </c>
       <c r="E4" t="n">
-        <v>1.7017</v>
+        <v>1.54</v>
       </c>
       <c r="F4" t="n">
-        <v>0.073</v>
+        <v>0.1605</v>
       </c>
       <c r="G4" t="n">
-        <v>1.7172</v>
+        <v>6.1021</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5629</v>
+        <v>3.0975</v>
       </c>
       <c r="I4" t="n">
-        <v>1.1542</v>
+        <v>3.0046</v>
       </c>
       <c r="J4" t="n">
-        <v>1.6838</v>
+        <v>7.4935</v>
       </c>
       <c r="K4" t="n">
-        <v>1.5718</v>
+        <v>5.267</v>
       </c>
       <c r="L4" t="n">
-        <v>0.112</v>
+        <v>2.2265</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0334</v>
+        <v>-1.3915</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.0089</v>
+        <v>-2.1695</v>
       </c>
       <c r="O4" t="n">
-        <v>1.0423</v>
+        <v>0.778</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.6805</v>
+        <v>-4.5526</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.1342</v>
+        <v>-5.9184</v>
       </c>
       <c r="R4" t="n">
-        <v>0.4537</v>
+        <v>1.3658</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1917</v>
+        <v>0.1511</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4869</v>
+        <v>-0.0351</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6787</v>
+        <v>0.1862</v>
       </c>
       <c r="V4" t="n">
-        <v>0.5463</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.639</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5483</v>
+        <v>1.6188</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0499</v>
+        <v>-0.056</v>
       </c>
       <c r="F5" t="n">
-        <v>1.4984</v>
+        <v>1.6748</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.8671</v>
+        <v>-0.8611</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.6695</v>
+        <v>-1.6687</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8024</v>
+        <v>0.8076</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.3422</v>
+        <v>-1.3497</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.4169</v>
+        <v>-1.4242</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M5" t="n">
-        <v>0.4751</v>
+        <v>0.4886</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.2526</v>
+        <v>-0.2446</v>
       </c>
       <c r="O5" t="n">
-        <v>0.7277</v>
+        <v>0.7331</v>
       </c>
       <c r="P5" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3493</v>
+        <v>0.4101</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2994</v>
+        <v>0.2042</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0499</v>
+        <v>0.2058</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9320000000000001</v>
+        <v>0.9317</v>
       </c>
       <c r="W5" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>T. SCRUBB</t>
+          <t>F. GUERRA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0287</v>
+        <v>1.312</v>
       </c>
       <c r="E6" t="n">
-        <v>3.2612</v>
+        <v>1.084</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.2325</v>
+        <v>0.228</v>
       </c>
       <c r="G6" t="n">
-        <v>1.1578</v>
+        <v>1.7184</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4301</v>
+        <v>0.7901</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7277</v>
+        <v>0.9283</v>
       </c>
       <c r="J6" t="n">
-        <v>2.0363</v>
+        <v>3.0088</v>
       </c>
       <c r="K6" t="n">
-        <v>2.0363</v>
+        <v>2.2268</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>0.782</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.8784999999999999</v>
+        <v>-1.2904</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.6062</v>
+        <v>-1.4367</v>
       </c>
       <c r="O6" t="n">
-        <v>0.7277</v>
+        <v>0.1463</v>
       </c>
       <c r="P6" t="n">
-        <v>0.4537</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-2.5039</v>
       </c>
       <c r="R6" t="n">
-        <v>0.4537</v>
+        <v>1.8211</v>
       </c>
       <c r="S6" t="n">
-        <v>1.7632</v>
+        <v>-0.2682</v>
       </c>
       <c r="T6" t="n">
-        <v>1.2249</v>
+        <v>-0.1233</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5383</v>
+        <v>-0.1449</v>
       </c>
       <c r="V6" t="n">
-        <v>-2.3461</v>
+        <v>0.5447</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.7025</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.3461</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. HUERTAS</t>
+          <t>A. DOORNEKAMP</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.957</v>
+        <v>1.2634</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9553</v>
+        <v>3.0326</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0018</v>
+        <v>-1.7691</v>
       </c>
       <c r="G7" t="n">
-        <v>6.127</v>
+        <v>1.0578</v>
       </c>
       <c r="H7" t="n">
-        <v>3.123</v>
+        <v>-1.098</v>
       </c>
       <c r="I7" t="n">
-        <v>3.0041</v>
+        <v>2.1558</v>
       </c>
       <c r="J7" t="n">
-        <v>7.5485</v>
+        <v>2.4637</v>
       </c>
       <c r="K7" t="n">
-        <v>5.3122</v>
+        <v>1.0859</v>
       </c>
       <c r="L7" t="n">
-        <v>2.2363</v>
+        <v>1.3778</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.4215</v>
+        <v>-1.4059</v>
       </c>
       <c r="N7" t="n">
-        <v>-2.1893</v>
+        <v>-2.1839</v>
       </c>
       <c r="O7" t="n">
-        <v>0.7678</v>
+        <v>0.778</v>
       </c>
       <c r="P7" t="n">
-        <v>-4.5367</v>
+        <v>0.9105</v>
       </c>
       <c r="Q7" t="n">
-        <v>-5.8976</v>
+        <v>-0.2276</v>
       </c>
       <c r="R7" t="n">
-        <v>1.361</v>
+        <v>1.1382</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.6333</v>
+        <v>-0.1601</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6956</v>
+        <v>-0.2929</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0623</v>
+        <v>0.1328</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-0.5447</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. DOORNEKAMP</t>
+          <t>B. FITIPALDO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9525</v>
+        <v>1.226</v>
       </c>
       <c r="E8" t="n">
-        <v>2.5723</v>
+        <v>2.1146</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.6199</v>
+        <v>-0.8885999999999999</v>
       </c>
       <c r="G8" t="n">
-        <v>1.0343</v>
+        <v>1.7345</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.1142</v>
+        <v>-0.2762</v>
       </c>
       <c r="I8" t="n">
-        <v>2.1485</v>
+        <v>2.0108</v>
       </c>
       <c r="J8" t="n">
-        <v>2.4717</v>
+        <v>2.2658</v>
       </c>
       <c r="K8" t="n">
-        <v>1.091</v>
+        <v>0.6722</v>
       </c>
       <c r="L8" t="n">
-        <v>1.3807</v>
+        <v>1.5935</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.4374</v>
+        <v>-0.5312</v>
       </c>
       <c r="N8" t="n">
-        <v>-2.2052</v>
+        <v>-0.9485</v>
       </c>
       <c r="O8" t="n">
-        <v>0.7678</v>
+        <v>0.4173</v>
       </c>
       <c r="P8" t="n">
-        <v>0.9073</v>
+        <v>0.4553</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1342</v>
+        <v>0.6829</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4428</v>
+        <v>0.2834</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.7652</v>
+        <v>0.0765</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3224</v>
+        <v>0.2069</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.5463</v>
+        <v>-1.2472</v>
       </c>
       <c r="W8" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.639</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="9">
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8364</v>
+        <v>1.0449</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.2541</v>
+        <v>-0.0682</v>
       </c>
       <c r="F9" t="n">
-        <v>1.0904</v>
+        <v>1.1131</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1408</v>
+        <v>0.1597</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.5817</v>
+        <v>-0.5721000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7224</v>
+        <v>0.7318</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3024</v>
+        <v>0.3013</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1905</v>
+        <v>0.1896</v>
       </c>
       <c r="L9" t="n">
-        <v>0.112</v>
+        <v>0.1117</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.1617</v>
+        <v>-0.1416</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.7721</v>
+        <v>-0.7617</v>
       </c>
       <c r="O9" t="n">
-        <v>0.6105</v>
+        <v>0.6201</v>
       </c>
       <c r="P9" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.8922</v>
+        <v>-0.7082000000000001</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5565</v>
+        <v>-0.3695</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3357</v>
+        <v>-0.3388</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>B. FITIPALDO</t>
+          <t>T. SCRUBB</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4759</v>
+        <v>0.169</v>
       </c>
       <c r="E10" t="n">
-        <v>1.7026</v>
+        <v>2.3729</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.2268</v>
+        <v>-2.2039</v>
       </c>
       <c r="G10" t="n">
-        <v>1.7292</v>
+        <v>1.1585</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2859</v>
+        <v>0.4253</v>
       </c>
       <c r="I10" t="n">
-        <v>2.0151</v>
+        <v>0.7331</v>
       </c>
       <c r="J10" t="n">
-        <v>2.2773</v>
+        <v>2.02</v>
       </c>
       <c r="K10" t="n">
-        <v>0.6754</v>
+        <v>2.02</v>
       </c>
       <c r="L10" t="n">
-        <v>1.6019</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.548</v>
+        <v>-0.8615</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.9612000000000001</v>
+        <v>-1.5946</v>
       </c>
       <c r="O10" t="n">
-        <v>0.4132</v>
+        <v>0.7331</v>
       </c>
       <c r="P10" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.2268</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.6805</v>
+        <v>0.4553</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4537</v>
+        <v>0.892</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3478</v>
+        <v>0.3529</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1059</v>
+        <v>0.5391</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.2534</v>
+        <v>-2.3367</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.2534</v>
+        <v>-2.3367</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.0772</v>
+        <v>-0.0736</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.9515</v>
+        <v>-0.3487</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.1257</v>
+        <v>0.2751</v>
       </c>
       <c r="G11" t="n">
-        <v>0.7206</v>
+        <v>0.6988</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.3504</v>
+        <v>-1.3608</v>
       </c>
       <c r="I11" t="n">
-        <v>2.071</v>
+        <v>2.0596</v>
       </c>
       <c r="J11" t="n">
-        <v>0.8286</v>
+        <v>0.7851</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.3574</v>
+        <v>-0.3834</v>
       </c>
       <c r="L11" t="n">
-        <v>1.186</v>
+        <v>1.1686</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.108</v>
+        <v>-0.0863</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.993</v>
+        <v>-0.9774</v>
       </c>
       <c r="O11" t="n">
-        <v>0.885</v>
+        <v>0.8911</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R11" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.1438</v>
+        <v>-0.1092</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7652</v>
+        <v>-0.1048</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3787</v>
+        <v>-0.0044</v>
       </c>
       <c r="V11" t="n">
-        <v>0.7071</v>
+        <v>0.7025</v>
       </c>
       <c r="W11" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>16.4386</v>
+        <v>17.1365</v>
       </c>
       <c r="E12" t="n">
-        <v>16.6237</v>
+        <v>17.0416</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.1853000000000005</v>
+        <v>0.09490000000000032</v>
       </c>
       <c r="G12" t="n">
-        <v>16.486</v>
+        <v>16.4881</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.4933</v>
+        <v>-1.5071</v>
       </c>
       <c r="I12" t="n">
-        <v>17.9791</v>
+        <v>17.9952</v>
       </c>
       <c r="J12" t="n">
-        <v>22.084</v>
+        <v>21.8646</v>
       </c>
       <c r="K12" t="n">
-        <v>10.796</v>
+        <v>10.6354</v>
       </c>
       <c r="L12" t="n">
-        <v>11.2881</v>
+        <v>11.2291</v>
       </c>
       <c r="M12" t="n">
-        <v>-5.598</v>
+        <v>-5.3764</v>
       </c>
       <c r="N12" t="n">
-        <v>-12.289</v>
+        <v>-12.1426</v>
       </c>
       <c r="O12" t="n">
-        <v>6.6912</v>
+        <v>6.7661</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.1342</v>
+        <v>-1.1381</v>
       </c>
       <c r="Q12" t="n">
-        <v>-12.4757</v>
+        <v>-12.5196</v>
       </c>
       <c r="R12" t="n">
-        <v>11.3418</v>
+        <v>11.3818</v>
       </c>
       <c r="S12" t="n">
-        <v>0.8618000000000003</v>
+        <v>1.5575</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4082999999999997</v>
+        <v>0.2997</v>
       </c>
       <c r="U12" t="n">
-        <v>1.2701</v>
+        <v>1.2574</v>
       </c>
       <c r="V12" t="n">
-        <v>0.2248999999999998</v>
+        <v>0.2291999999999997</v>
       </c>
       <c r="W12" t="n">
-        <v>7.4239</v>
+        <v>7.3971</v>
       </c>
       <c r="X12" t="n">
-        <v>-7.1989</v>
+        <v>-7.1679</v>
       </c>
     </row>
     <row r="13">
@@ -1423,64 +1423,64 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.4378</v>
+        <v>3.7146</v>
       </c>
       <c r="E13" t="n">
-        <v>5.4798</v>
+        <v>5.5336</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.042</v>
+        <v>-1.8191</v>
       </c>
       <c r="G13" t="n">
-        <v>2.9352</v>
+        <v>2.91</v>
       </c>
       <c r="H13" t="n">
-        <v>3.423</v>
+        <v>3.4017</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.4878</v>
+        <v>-0.4917</v>
       </c>
       <c r="J13" t="n">
-        <v>6.3212</v>
+        <v>6.2647</v>
       </c>
       <c r="K13" t="n">
-        <v>4.9832</v>
+        <v>4.9395</v>
       </c>
       <c r="L13" t="n">
-        <v>1.338</v>
+        <v>1.3252</v>
       </c>
       <c r="M13" t="n">
-        <v>-3.386</v>
+        <v>-3.3547</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.5602</v>
+        <v>-1.5378</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.8258</v>
+        <v>-1.8169</v>
       </c>
       <c r="P13" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R13" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.4313</v>
+        <v>-0.1255</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1875</v>
+        <v>-0.0678</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2438</v>
+        <v>-0.0578</v>
       </c>
       <c r="V13" t="n">
-        <v>0.7071</v>
+        <v>0.7025</v>
       </c>
       <c r="W13" t="n">
-        <v>0.7071</v>
+        <v>0.7025</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.001</v>
+        <v>0.5104</v>
       </c>
       <c r="E14" t="n">
-        <v>3.6715</v>
+        <v>2.1265</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.6705</v>
+        <v>-1.6161</v>
       </c>
       <c r="G14" t="n">
-        <v>0.702</v>
+        <v>0.7026</v>
       </c>
       <c r="H14" t="n">
-        <v>0.9019</v>
+        <v>0.8991</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1999</v>
+        <v>-0.1965</v>
       </c>
       <c r="J14" t="n">
-        <v>1.7646</v>
+        <v>1.7497</v>
       </c>
       <c r="K14" t="n">
-        <v>1.6899</v>
+        <v>1.6752</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.0626</v>
+        <v>-1.0471</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.788</v>
+        <v>-0.7761</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.2745</v>
+        <v>-0.271</v>
       </c>
       <c r="P14" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R14" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S14" t="n">
-        <v>2.6431</v>
+        <v>1.1461</v>
       </c>
       <c r="T14" t="n">
-        <v>2.5194</v>
+        <v>0.9913999999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1237</v>
+        <v>0.1546</v>
       </c>
       <c r="V14" t="n">
-        <v>-2.0246</v>
+        <v>-2.0212</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.3856</v>
+        <v>-0.387</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D. CACOK</t>
+          <t>D. ENNIS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4689</v>
+        <v>0.4912</v>
       </c>
       <c r="E15" t="n">
-        <v>1.2164</v>
+        <v>1.2658</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.7476</v>
+        <v>-0.7747000000000001</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.0174</v>
+        <v>-0.4948</v>
       </c>
       <c r="H15" t="n">
-        <v>1.5179</v>
+        <v>-0.8851</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.5353</v>
+        <v>0.3903</v>
       </c>
       <c r="J15" t="n">
-        <v>2.4124</v>
+        <v>1.3984</v>
       </c>
       <c r="K15" t="n">
-        <v>2.3378</v>
+        <v>0.2068</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0746</v>
+        <v>1.1916</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.4298</v>
+        <v>-1.8932</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.8198</v>
+        <v>-1.092</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.6099</v>
+        <v>-0.8012</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.8147</v>
+        <v>1.1382</v>
       </c>
       <c r="Q15" t="n">
-        <v>-3.4025</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5878</v>
+        <v>1.1382</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1155</v>
+        <v>-0.1522</v>
       </c>
       <c r="T15" t="n">
-        <v>0.0212</v>
+        <v>-0.1326</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0944</v>
+        <v>-0.0196</v>
       </c>
       <c r="V15" t="n">
-        <v>2.1853</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>2.1853</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1657,22 +1657,22 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1891</v>
+        <v>0.2234</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.0696</v>
+        <v>-0.0697</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2586</v>
+        <v>0.2931</v>
       </c>
       <c r="G16" t="n">
-        <v>0.09859999999999999</v>
+        <v>0.1014</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4718</v>
+        <v>0.4738</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3732</v>
+        <v>-0.3724</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1684,31 +1684,31 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0.09859999999999999</v>
+        <v>0.1014</v>
       </c>
       <c r="N16" t="n">
-        <v>0.4718</v>
+        <v>0.4738</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.3732</v>
+        <v>-0.3724</v>
       </c>
       <c r="P16" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1364</v>
+        <v>-0.1057</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.0696</v>
+        <v>-0.0697</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0668</v>
+        <v>-0.0359</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. ENNIS</t>
+          <t>D. CACOK</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.154</v>
+        <v>0.0499</v>
       </c>
       <c r="E17" t="n">
-        <v>0.915</v>
+        <v>0.8335</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.761</v>
+        <v>-0.7836</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.5056</v>
+        <v>-0.006</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.8948</v>
+        <v>1.522</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3892</v>
+        <v>-1.528</v>
       </c>
       <c r="J17" t="n">
-        <v>1.4019</v>
+        <v>2.4014</v>
       </c>
       <c r="K17" t="n">
-        <v>0.2078</v>
+        <v>2.327</v>
       </c>
       <c r="L17" t="n">
-        <v>1.1941</v>
+        <v>0.0745</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.9075</v>
+        <v>-2.4075</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.1026</v>
+        <v>-0.805</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.805</v>
+        <v>-1.6025</v>
       </c>
       <c r="P17" t="n">
-        <v>1.1342</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-3.4145</v>
       </c>
       <c r="R17" t="n">
-        <v>1.1342</v>
+        <v>1.5934</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4745</v>
+        <v>-0.302</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4869</v>
+        <v>-0.3324</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0124</v>
+        <v>0.0305</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>2.1789</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>2.1789</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>T. NAKIC</t>
+          <t>M. DIAGNE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,58 +1813,58 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.8307</v>
+        <v>-0.9926</v>
       </c>
       <c r="E18" t="n">
-        <v>1.977</v>
+        <v>0.0315</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.8077</v>
+        <v>-1.024</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.2407</v>
+        <v>-0.6081</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6654</v>
+        <v>-0.2357</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.5753</v>
+        <v>-0.3724</v>
       </c>
       <c r="J18" t="n">
-        <v>1.239</v>
+        <v>0.3103</v>
       </c>
       <c r="K18" t="n">
-        <v>0.8312</v>
+        <v>0.3103</v>
       </c>
       <c r="L18" t="n">
-        <v>0.4078</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-3.4797</v>
+        <v>-0.9184</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.4966</v>
+        <v>-0.546</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.9831</v>
+        <v>-0.3724</v>
       </c>
       <c r="P18" t="n">
-        <v>1.1342</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1342</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0.2758</v>
+        <v>-0.3845</v>
       </c>
       <c r="T18" t="n">
-        <v>0.738</v>
+        <v>-0.2788</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4621</v>
+        <v>-0.1057</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. DIAGNE</t>
+          <t>T. NAKIC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,58 +1891,58 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.0274</v>
+        <v>-1.1503</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0335</v>
+        <v>1.3799</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.0609</v>
+        <v>-2.5302</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.6128</v>
+        <v>-2.2256</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.2396</v>
+        <v>-0.6526999999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.3732</v>
+        <v>-1.5729</v>
       </c>
       <c r="J19" t="n">
-        <v>0.3117</v>
+        <v>1.2293</v>
       </c>
       <c r="K19" t="n">
-        <v>0.3117</v>
+        <v>0.8274</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>0.4019</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.9245</v>
+        <v>-3.4549</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.5513</v>
+        <v>-1.48</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.3732</v>
+        <v>-1.9749</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1.1382</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.1382</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4146</v>
+        <v>-0.0629</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2782</v>
+        <v>0.1506</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1364</v>
+        <v>-0.2135</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.5847</v>
+        <v>-2.2394</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.206</v>
+        <v>-0.5508999999999999</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.3786</v>
+        <v>-1.6885</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.6217</v>
+        <v>-3.638</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.2177</v>
+        <v>-0.2264</v>
       </c>
       <c r="I20" t="n">
-        <v>-3.4039</v>
+        <v>-3.4116</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.6029</v>
+        <v>-1.6437</v>
       </c>
       <c r="K20" t="n">
-        <v>1.4679</v>
+        <v>1.4404</v>
       </c>
       <c r="L20" t="n">
-        <v>-3.0708</v>
+        <v>-3.0841</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.0188</v>
+        <v>-1.9943</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.6857</v>
+        <v>-1.6668</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.3331</v>
+        <v>-0.3275</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R20" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2144</v>
+        <v>0.1498</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.9739</v>
+        <v>-0.2652</v>
       </c>
       <c r="U20" t="n">
-        <v>0.7594</v>
+        <v>0.4149</v>
       </c>
       <c r="V20" t="n">
-        <v>1.4783</v>
+        <v>1.4764</v>
       </c>
       <c r="W20" t="n">
-        <v>2.7317</v>
+        <v>2.7237</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="21">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.8731</v>
+        <v>-2.6204</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.3613</v>
+        <v>-1.2481</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.5118</v>
+        <v>-1.3723</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.5161</v>
+        <v>-1.51</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.6711</v>
+        <v>-0.6637999999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.845</v>
+        <v>-0.8462</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.7171</v>
+        <v>-0.7207</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0693</v>
+        <v>0.0689</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.7864</v>
+        <v>-0.7896</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.799</v>
+        <v>-0.7893</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.7403999999999999</v>
+        <v>-0.7328</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.0586</v>
+        <v>-0.0565</v>
       </c>
       <c r="P21" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R21" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4912</v>
+        <v>-0.2486</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4174</v>
+        <v>-0.2998</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0738</v>
+        <v>0.0512</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="22">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.2867</v>
+        <v>-3.0796</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.8299</v>
+        <v>-0.747</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.4569</v>
+        <v>-2.3326</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.4072</v>
+        <v>-2.4102</v>
       </c>
       <c r="H22" t="n">
-        <v>0.3276</v>
+        <v>0.3247</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.7348</v>
+        <v>-2.7349</v>
       </c>
       <c r="J22" t="n">
-        <v>0.0116</v>
+        <v>-0.0159</v>
       </c>
       <c r="K22" t="n">
-        <v>1.5097</v>
+        <v>1.4889</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.4981</v>
+        <v>-1.5048</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.4188</v>
+        <v>-2.3943</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.1821</v>
+        <v>-1.1642</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.2368</v>
+        <v>-1.2301</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R22" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2671</v>
+        <v>-0.0547</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1875</v>
+        <v>-0.0678</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0796</v>
+        <v>0.013</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.3856</v>
+        <v>-0.387</v>
       </c>
       <c r="W22" t="n">
-        <v>0.7071</v>
+        <v>0.7025</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="23">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.7804</v>
+        <v>-4.4165</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.6982</v>
+        <v>-4.0253</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.0822</v>
+        <v>-0.3911</v>
       </c>
       <c r="G23" t="n">
-        <v>-5.1588</v>
+        <v>-5.1609</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.1818</v>
+        <v>-1.1805</v>
       </c>
       <c r="I23" t="n">
-        <v>-3.977</v>
+        <v>-3.9804</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.6814</v>
+        <v>-2.7101</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.4715</v>
+        <v>-0.4901</v>
       </c>
       <c r="L23" t="n">
-        <v>-2.2098</v>
+        <v>-2.22</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.4774</v>
+        <v>-2.4508</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.7103</v>
+        <v>-0.6904</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.7672</v>
+        <v>-1.7604</v>
       </c>
       <c r="P23" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R23" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.529</v>
+        <v>-0.1661</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.0434</v>
+        <v>-0.3349</v>
       </c>
       <c r="U23" t="n">
-        <v>0.5144</v>
+        <v>0.1688</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-7.3062</v>
+        <v>-6.9303</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.943</v>
+        <v>-4.6247</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.3632</v>
+        <v>-2.3056</v>
       </c>
       <c r="G24" t="n">
-        <v>-4.1415</v>
+        <v>-4.1486</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.2786</v>
+        <v>-1.2699</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.8629</v>
+        <v>-2.8786</v>
       </c>
       <c r="J24" t="n">
-        <v>-2.863</v>
+        <v>-2.8871</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.6478</v>
+        <v>-0.6516999999999999</v>
       </c>
       <c r="L24" t="n">
-        <v>-2.2152</v>
+        <v>-2.2353</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.2785</v>
+        <v>-1.2615</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.6308</v>
+        <v>-0.6182</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.6477000000000001</v>
+        <v>-0.6433</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R24" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.9379</v>
+        <v>-0.5541</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.9043</v>
+        <v>-0.5508</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.0336</v>
+        <v>-0.0033</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W24" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X24" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-16.4384</v>
+        <v>-16.4396</v>
       </c>
       <c r="E25" t="n">
-        <v>0.1851999999999983</v>
+        <v>-0.09489999999999998</v>
       </c>
       <c r="F25" t="n">
-        <v>-16.6238</v>
+        <v>-16.3447</v>
       </c>
       <c r="G25" t="n">
-        <v>-16.486</v>
+        <v>-16.4882</v>
       </c>
       <c r="H25" t="n">
-        <v>1.4932</v>
+        <v>1.507199999999999</v>
       </c>
       <c r="I25" t="n">
-        <v>-17.9791</v>
+        <v>-17.9953</v>
       </c>
       <c r="J25" t="n">
-        <v>5.598000000000001</v>
+        <v>5.376299999999999</v>
       </c>
       <c r="K25" t="n">
-        <v>12.2892</v>
+        <v>12.1426</v>
       </c>
       <c r="L25" t="n">
-        <v>-6.6912</v>
+        <v>-6.7661</v>
       </c>
       <c r="M25" t="n">
-        <v>-22.084</v>
+        <v>-21.8646</v>
       </c>
       <c r="N25" t="n">
-        <v>-10.796</v>
+        <v>-10.6355</v>
       </c>
       <c r="O25" t="n">
-        <v>-11.2881</v>
+        <v>-11.2291</v>
       </c>
       <c r="P25" t="n">
-        <v>1.134100000000001</v>
+        <v>1.1381</v>
       </c>
       <c r="Q25" t="n">
-        <v>-11.3416</v>
+        <v>-11.3816</v>
       </c>
       <c r="R25" t="n">
-        <v>12.4759</v>
+        <v>12.5199</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.8620000000000001</v>
+        <v>-0.8604000000000001</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.2701</v>
+        <v>-1.2578</v>
       </c>
       <c r="U25" t="n">
-        <v>0.4082</v>
+        <v>0.3971999999999999</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.2249000000000001</v>
+        <v>-0.2293999999999996</v>
       </c>
       <c r="W25" t="n">
-        <v>7.199</v>
+        <v>7.167899999999999</v>
       </c>
       <c r="X25" t="n">
-        <v>-7.4238</v>
+        <v>-7.3971</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104478_W3.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104478_W3.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104478_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104478_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104478_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104478_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104478_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104478_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104478_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104478_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-2.3367</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104478_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104478_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,7 @@
       <c r="X12" t="n">
         <v>-7.1679</v>
       </c>
+      <c r="Y12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1541,11 @@
       <c r="X13" t="n">
         <v>0</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104478_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104478_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>0</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104478_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104478_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104478_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104478_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104478_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104478_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104478_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104478_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104478_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104478_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,7 @@
       <c r="X25" t="n">
         <v>-7.3971</v>
       </c>
+      <c r="Y25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
